--- a/sitepreview/trust/1.4.0/ValueSet-KeyUsage-UAT.xlsx
+++ b/sitepreview/trust/1.4.0/ValueSet-KeyUsage-UAT.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T19:59:39+00:00</t>
+    <t>2026-02-04T20:34:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
